--- a/BWI/bestwine_output/bestwine_Argentina.xlsx
+++ b/BWI/bestwine_output/bestwine_Argentina.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA337"/>
+  <dimension ref="A1:AA338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -32982,6 +32982,95 @@
       <c r="Z337" s="2" t="inlineStr"/>
       <c r="AA337" s="2" t="inlineStr"/>
     </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>Digimpex Srl</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>Digimpex Srl</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>46195</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>Wilde</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>6224 Mariano Moreno</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="inlineStr">
+        <is>
+          <t>B1875</t>
+        </is>
+      </c>
+      <c r="I338" s="2" t="inlineStr">
+        <is>
+          <t>https://digimpex.com</t>
+        </is>
+      </c>
+      <c r="J338" s="2" t="inlineStr"/>
+      <c r="K338" s="2" t="inlineStr"/>
+      <c r="L338" s="2" t="inlineStr"/>
+      <c r="M338" s="2" t="inlineStr"/>
+      <c r="N338" s="2" t="inlineStr">
+        <is>
+          <t>digimpex@gmail.com</t>
+        </is>
+      </c>
+      <c r="O338" s="2" t="inlineStr">
+        <is>
+          <t>+54 11 4206-1087</t>
+        </is>
+      </c>
+      <c r="P338" s="2" t="inlineStr"/>
+      <c r="Q338" s="2" t="inlineStr"/>
+      <c r="R338" s="2" t="inlineStr"/>
+      <c r="S338" s="2" t="inlineStr"/>
+      <c r="T338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/digimpexsrl</t>
+        </is>
+      </c>
+      <c r="U338" s="2" t="inlineStr"/>
+      <c r="V338" s="2" t="inlineStr"/>
+      <c r="W338" s="2" t="inlineStr">
+        <is>
+          <t>Marco Di Meo</t>
+        </is>
+      </c>
+      <c r="X338" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y338" s="2" t="inlineStr"/>
+      <c r="Z338" s="2" t="inlineStr"/>
+      <c r="AA338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marco-di-meo-55144b35/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Argentina.xlsx
+++ b/BWI/bestwine_output/bestwine_Argentina.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA338"/>
+  <dimension ref="A1:AA342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -33071,6 +33071,422 @@
         </is>
       </c>
     </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>Espaciovino S.r.l.</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>Espaciovino</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>CABA</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>Santo Tomé 3852</t>
+        </is>
+      </c>
+      <c r="H339" s="2" t="inlineStr">
+        <is>
+          <t>C1417</t>
+        </is>
+      </c>
+      <c r="I339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.espaciovino.com.ar</t>
+        </is>
+      </c>
+      <c r="J339" s="2" t="inlineStr"/>
+      <c r="K339" s="2" t="inlineStr"/>
+      <c r="L339" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M339" s="2" t="inlineStr"/>
+      <c r="N339" s="2" t="inlineStr">
+        <is>
+          <t>info@espaciovino.com.ar</t>
+        </is>
+      </c>
+      <c r="O339" s="2" t="inlineStr">
+        <is>
+          <t>+54 11 5352-8466</t>
+        </is>
+      </c>
+      <c r="P339" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q339" s="2" t="inlineStr">
+        <is>
+          <t>30-71564031-3</t>
+        </is>
+      </c>
+      <c r="R339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/espaciovino-com/</t>
+        </is>
+      </c>
+      <c r="S339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/espaciovino/</t>
+        </is>
+      </c>
+      <c r="T339" s="2" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/espaciovino</t>
+        </is>
+      </c>
+      <c r="U339" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/espaciovino</t>
+        </is>
+      </c>
+      <c r="V339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@espaciovinoAr/</t>
+        </is>
+      </c>
+      <c r="W339" s="2" t="inlineStr">
+        <is>
+          <t>Martin Fernandez</t>
+        </is>
+      </c>
+      <c r="X339" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="Y339" s="2" t="inlineStr"/>
+      <c r="Z339" s="2" t="inlineStr"/>
+      <c r="AA339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/martinf/</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>Espaciovino S.r.l.</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>Espaciovino</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>CABA</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>Santo Tomé 3852</t>
+        </is>
+      </c>
+      <c r="H340" s="2" t="inlineStr">
+        <is>
+          <t>C1417</t>
+        </is>
+      </c>
+      <c r="I340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.espaciovino.com.ar</t>
+        </is>
+      </c>
+      <c r="J340" s="2" t="inlineStr"/>
+      <c r="K340" s="2" t="inlineStr"/>
+      <c r="L340" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M340" s="2" t="inlineStr"/>
+      <c r="N340" s="2" t="inlineStr">
+        <is>
+          <t>info@espaciovino.com.ar</t>
+        </is>
+      </c>
+      <c r="O340" s="2" t="inlineStr">
+        <is>
+          <t>+54 11 5352-8466</t>
+        </is>
+      </c>
+      <c r="P340" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q340" s="2" t="inlineStr">
+        <is>
+          <t>30-71564031-3</t>
+        </is>
+      </c>
+      <c r="R340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/espaciovino-com/</t>
+        </is>
+      </c>
+      <c r="S340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/espaciovino/</t>
+        </is>
+      </c>
+      <c r="T340" s="2" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/espaciovino</t>
+        </is>
+      </c>
+      <c r="U340" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/espaciovino</t>
+        </is>
+      </c>
+      <c r="V340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@espaciovinoAr/</t>
+        </is>
+      </c>
+      <c r="W340" s="2" t="inlineStr">
+        <is>
+          <t>Diego Fernández</t>
+        </is>
+      </c>
+      <c r="X340" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Y340" s="2" t="inlineStr"/>
+      <c r="Z340" s="2" t="inlineStr"/>
+      <c r="AA340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/diego-fern%C3%A1ndez-058b3b95/</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>Little Italia Market</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>Little Italia Market</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>122576</t>
+        </is>
+      </c>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="inlineStr">
+        <is>
+          <t>Autonomous City of Buenos Aires</t>
+        </is>
+      </c>
+      <c r="G341" s="2" t="inlineStr">
+        <is>
+          <t>2701 Doctor Rómulo Naón</t>
+        </is>
+      </c>
+      <c r="H341" s="2" t="inlineStr">
+        <is>
+          <t>C1430</t>
+        </is>
+      </c>
+      <c r="I341" s="2" t="inlineStr">
+        <is>
+          <t>https://littleitaliamarket.com.ar</t>
+        </is>
+      </c>
+      <c r="J341" s="2" t="inlineStr"/>
+      <c r="K341" s="2" t="inlineStr"/>
+      <c r="L341" s="2" t="inlineStr"/>
+      <c r="M341" s="2" t="inlineStr"/>
+      <c r="N341" s="2" t="inlineStr">
+        <is>
+          <t>italianmarket20@gmail.com</t>
+        </is>
+      </c>
+      <c r="O341" s="2" t="inlineStr">
+        <is>
+          <t>+54 11 3132-8558</t>
+        </is>
+      </c>
+      <c r="P341" s="2" t="inlineStr"/>
+      <c r="Q341" s="2" t="inlineStr"/>
+      <c r="R341" s="2" t="inlineStr"/>
+      <c r="S341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Littleitaliamarket/</t>
+        </is>
+      </c>
+      <c r="T341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/littleitaliamarket/</t>
+        </is>
+      </c>
+      <c r="U341" s="2" t="inlineStr"/>
+      <c r="V341" s="2" t="inlineStr"/>
+      <c r="W341" s="2" t="inlineStr">
+        <is>
+          <t>Luciano Arias</t>
+        </is>
+      </c>
+      <c r="X341" s="2" t="inlineStr">
+        <is>
+          <t>Sales Specialist</t>
+        </is>
+      </c>
+      <c r="Y341" s="2" t="inlineStr"/>
+      <c r="Z341" s="2" t="inlineStr"/>
+      <c r="AA341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luciano-arias-a80066274/</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>Digimpex Srl</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>Digimpex Srl</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>46195</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>Wilde</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>6224 Mariano Moreno</t>
+        </is>
+      </c>
+      <c r="H342" s="2" t="inlineStr">
+        <is>
+          <t>B1875</t>
+        </is>
+      </c>
+      <c r="I342" s="2" t="inlineStr">
+        <is>
+          <t>https://digimpex.com</t>
+        </is>
+      </c>
+      <c r="J342" s="2" t="inlineStr"/>
+      <c r="K342" s="2" t="inlineStr"/>
+      <c r="L342" s="2" t="inlineStr"/>
+      <c r="M342" s="2" t="inlineStr"/>
+      <c r="N342" s="2" t="inlineStr">
+        <is>
+          <t>digimpex@gmail.com</t>
+        </is>
+      </c>
+      <c r="O342" s="2" t="inlineStr">
+        <is>
+          <t>+54 11 4206-1087</t>
+        </is>
+      </c>
+      <c r="P342" s="2" t="inlineStr"/>
+      <c r="Q342" s="2" t="inlineStr"/>
+      <c r="R342" s="2" t="inlineStr"/>
+      <c r="S342" s="2" t="inlineStr"/>
+      <c r="T342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/digimpexsrl</t>
+        </is>
+      </c>
+      <c r="U342" s="2" t="inlineStr"/>
+      <c r="V342" s="2" t="inlineStr"/>
+      <c r="W342" s="2" t="inlineStr">
+        <is>
+          <t>Marco Di Meo</t>
+        </is>
+      </c>
+      <c r="X342" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y342" s="2" t="inlineStr"/>
+      <c r="Z342" s="2" t="inlineStr"/>
+      <c r="AA342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marco-di-meo-55144b35/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Argentina.xlsx
+++ b/BWI/bestwine_output/bestwine_Argentina.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA342"/>
+  <dimension ref="A1:AA347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -33487,6 +33487,499 @@
         </is>
       </c>
     </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>Azari Wines</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr"/>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>168921</t>
+        </is>
+      </c>
+      <c r="D343" s="2" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="inlineStr"/>
+      <c r="G343" s="2" t="inlineStr">
+        <is>
+          <t>Cuzco 770</t>
+        </is>
+      </c>
+      <c r="H343" s="2" t="inlineStr">
+        <is>
+          <t>C1408</t>
+        </is>
+      </c>
+      <c r="I343" s="2" t="inlineStr">
+        <is>
+          <t>https://www.azariwines.com.ar</t>
+        </is>
+      </c>
+      <c r="J343" s="2" t="inlineStr"/>
+      <c r="K343" s="2" t="inlineStr"/>
+      <c r="L343" s="2" t="inlineStr"/>
+      <c r="M343" s="2" t="inlineStr"/>
+      <c r="N343" s="2" t="inlineStr">
+        <is>
+          <t>Azariwines@gmail.com</t>
+        </is>
+      </c>
+      <c r="O343" s="2" t="inlineStr">
+        <is>
+          <t>+54 11 4180-8164</t>
+        </is>
+      </c>
+      <c r="P343" s="2" t="inlineStr"/>
+      <c r="Q343" s="2" t="inlineStr"/>
+      <c r="R343" s="2" t="inlineStr"/>
+      <c r="S343" s="2" t="inlineStr"/>
+      <c r="T343" s="2" t="inlineStr"/>
+      <c r="U343" s="2" t="inlineStr"/>
+      <c r="V343" s="2" t="inlineStr"/>
+      <c r="W343" s="2" t="inlineStr">
+        <is>
+          <t>Bruno Grillo</t>
+        </is>
+      </c>
+      <c r="X343" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y343" s="2" t="inlineStr"/>
+      <c r="Z343" s="2" t="inlineStr"/>
+      <c r="AA343" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bruno-grillo-681432151/</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>Espaciovino S.r.l.</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>Espaciovino</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr">
+        <is>
+          <t>CABA</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="G344" s="2" t="inlineStr">
+        <is>
+          <t>Santo Tomé 3852</t>
+        </is>
+      </c>
+      <c r="H344" s="2" t="inlineStr">
+        <is>
+          <t>C1417</t>
+        </is>
+      </c>
+      <c r="I344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.espaciovino.com.ar</t>
+        </is>
+      </c>
+      <c r="J344" s="2" t="inlineStr"/>
+      <c r="K344" s="2" t="inlineStr"/>
+      <c r="L344" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M344" s="2" t="inlineStr"/>
+      <c r="N344" s="2" t="inlineStr">
+        <is>
+          <t>info@espaciovino.com.ar</t>
+        </is>
+      </c>
+      <c r="O344" s="2" t="inlineStr">
+        <is>
+          <t>+54 11 5352-8466</t>
+        </is>
+      </c>
+      <c r="P344" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q344" s="2" t="inlineStr">
+        <is>
+          <t>30-71564031-3</t>
+        </is>
+      </c>
+      <c r="R344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/espaciovino-com/</t>
+        </is>
+      </c>
+      <c r="S344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/espaciovino/</t>
+        </is>
+      </c>
+      <c r="T344" s="2" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/espaciovino</t>
+        </is>
+      </c>
+      <c r="U344" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/espaciovino</t>
+        </is>
+      </c>
+      <c r="V344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@espaciovinoAr/</t>
+        </is>
+      </c>
+      <c r="W344" s="2" t="inlineStr">
+        <is>
+          <t>Martin Fernandez</t>
+        </is>
+      </c>
+      <c r="X344" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="Y344" s="2" t="inlineStr"/>
+      <c r="Z344" s="2" t="inlineStr"/>
+      <c r="AA344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/martinf/</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>Espaciovino S.r.l.</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>Espaciovino</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D345" s="2" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>CABA</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>Santo Tomé 3852</t>
+        </is>
+      </c>
+      <c r="H345" s="2" t="inlineStr">
+        <is>
+          <t>C1417</t>
+        </is>
+      </c>
+      <c r="I345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.espaciovino.com.ar</t>
+        </is>
+      </c>
+      <c r="J345" s="2" t="inlineStr"/>
+      <c r="K345" s="2" t="inlineStr"/>
+      <c r="L345" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M345" s="2" t="inlineStr"/>
+      <c r="N345" s="2" t="inlineStr">
+        <is>
+          <t>info@espaciovino.com.ar</t>
+        </is>
+      </c>
+      <c r="O345" s="2" t="inlineStr">
+        <is>
+          <t>+54 11 5352-8466</t>
+        </is>
+      </c>
+      <c r="P345" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q345" s="2" t="inlineStr">
+        <is>
+          <t>30-71564031-3</t>
+        </is>
+      </c>
+      <c r="R345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/espaciovino-com/</t>
+        </is>
+      </c>
+      <c r="S345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/espaciovino/</t>
+        </is>
+      </c>
+      <c r="T345" s="2" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/espaciovino</t>
+        </is>
+      </c>
+      <c r="U345" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/espaciovino</t>
+        </is>
+      </c>
+      <c r="V345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@espaciovinoAr/</t>
+        </is>
+      </c>
+      <c r="W345" s="2" t="inlineStr">
+        <is>
+          <t>Diego Fernández</t>
+        </is>
+      </c>
+      <c r="X345" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Y345" s="2" t="inlineStr"/>
+      <c r="Z345" s="2" t="inlineStr"/>
+      <c r="AA345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/diego-fern%C3%A1ndez-058b3b95/</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>Little Italia Market</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>Little Italia Market</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>122576</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>Autonomous City of Buenos Aires</t>
+        </is>
+      </c>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>2701 Doctor Rómulo Naón</t>
+        </is>
+      </c>
+      <c r="H346" s="2" t="inlineStr">
+        <is>
+          <t>C1430</t>
+        </is>
+      </c>
+      <c r="I346" s="2" t="inlineStr">
+        <is>
+          <t>https://littleitaliamarket.com.ar</t>
+        </is>
+      </c>
+      <c r="J346" s="2" t="inlineStr"/>
+      <c r="K346" s="2" t="inlineStr"/>
+      <c r="L346" s="2" t="inlineStr"/>
+      <c r="M346" s="2" t="inlineStr"/>
+      <c r="N346" s="2" t="inlineStr">
+        <is>
+          <t>italianmarket20@gmail.com</t>
+        </is>
+      </c>
+      <c r="O346" s="2" t="inlineStr">
+        <is>
+          <t>+54 11 3132-8558</t>
+        </is>
+      </c>
+      <c r="P346" s="2" t="inlineStr"/>
+      <c r="Q346" s="2" t="inlineStr"/>
+      <c r="R346" s="2" t="inlineStr"/>
+      <c r="S346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Littleitaliamarket/</t>
+        </is>
+      </c>
+      <c r="T346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/littleitaliamarket/</t>
+        </is>
+      </c>
+      <c r="U346" s="2" t="inlineStr"/>
+      <c r="V346" s="2" t="inlineStr"/>
+      <c r="W346" s="2" t="inlineStr">
+        <is>
+          <t>Luciano Arias</t>
+        </is>
+      </c>
+      <c r="X346" s="2" t="inlineStr">
+        <is>
+          <t>Sales Specialist</t>
+        </is>
+      </c>
+      <c r="Y346" s="2" t="inlineStr"/>
+      <c r="Z346" s="2" t="inlineStr"/>
+      <c r="AA346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luciano-arias-a80066274/</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>Digimpex Srl</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>Digimpex Srl</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>46195</t>
+        </is>
+      </c>
+      <c r="D347" s="2" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="E347" s="2" t="inlineStr">
+        <is>
+          <t>Wilde</t>
+        </is>
+      </c>
+      <c r="F347" s="2" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="G347" s="2" t="inlineStr">
+        <is>
+          <t>6224 Mariano Moreno</t>
+        </is>
+      </c>
+      <c r="H347" s="2" t="inlineStr">
+        <is>
+          <t>B1875</t>
+        </is>
+      </c>
+      <c r="I347" s="2" t="inlineStr">
+        <is>
+          <t>https://digimpex.com</t>
+        </is>
+      </c>
+      <c r="J347" s="2" t="inlineStr"/>
+      <c r="K347" s="2" t="inlineStr"/>
+      <c r="L347" s="2" t="inlineStr"/>
+      <c r="M347" s="2" t="inlineStr"/>
+      <c r="N347" s="2" t="inlineStr">
+        <is>
+          <t>digimpex@gmail.com</t>
+        </is>
+      </c>
+      <c r="O347" s="2" t="inlineStr">
+        <is>
+          <t>+54 11 4206-1087</t>
+        </is>
+      </c>
+      <c r="P347" s="2" t="inlineStr"/>
+      <c r="Q347" s="2" t="inlineStr"/>
+      <c r="R347" s="2" t="inlineStr"/>
+      <c r="S347" s="2" t="inlineStr"/>
+      <c r="T347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/digimpexsrl</t>
+        </is>
+      </c>
+      <c r="U347" s="2" t="inlineStr"/>
+      <c r="V347" s="2" t="inlineStr"/>
+      <c r="W347" s="2" t="inlineStr">
+        <is>
+          <t>Marco Di Meo</t>
+        </is>
+      </c>
+      <c r="X347" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y347" s="2" t="inlineStr"/>
+      <c r="Z347" s="2" t="inlineStr"/>
+      <c r="AA347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marco-di-meo-55144b35/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
